--- a/exports/events.xlsx
+++ b/exports/events.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,10 +457,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -469,30 +469,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-15 12:59:03</t>
+          <t>2025-08-19 12:49:41</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-08-15 12:59:01</t>
+          <t>2025-08-19 12:47:41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -503,42 +503,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-08-15 12:58:38</t>
+          <t>2025-08-19 12:47:39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-08-15 12:57:35</t>
+          <t>2025-08-19 12:47:37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -549,65 +549,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-08-15 12:57:27</t>
+          <t>2025-08-19 12:47:36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-08-15 12:57:25</t>
+          <t>2025-08-19 12:47:30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-08-15 12:57:21</t>
+          <t>2025-08-19 12:47:30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -618,19 +618,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-08-15 12:57:13</t>
+          <t>2025-08-19 12:47:25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -641,33 +641,33 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-08-15 12:57:09</t>
+          <t>2025-08-19 12:47:23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -676,21 +676,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-08-15 12:57:06</t>
+          <t>2025-08-19 12:47:22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-08-15 12:57:04</t>
+          <t>2025-08-19 12:47:16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -710,10 +710,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -722,21 +722,21 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-08-15 12:57:02</t>
+          <t>2025-08-19 12:47:15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -745,21 +745,21 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-08-15 12:56:53</t>
+          <t>2025-08-19 12:47:10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-08-15 12:56:50</t>
+          <t>2025-08-19 12:47:10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -779,19 +779,19 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-08-15 12:56:48</t>
+          <t>2025-08-19 12:44:48</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -802,42 +802,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-08-15 12:56:46</t>
+          <t>2025-08-19 12:44:47</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-08-15 12:56:44</t>
+          <t>2025-08-19 12:41:53</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -848,369 +848,24 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kamera 1</t>
+          <t>Kamera 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-08-15 12:56:35</t>
+          <t>2025-08-19 12:41:52</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>38</v>
-      </c>
-      <c r="B20" t="n">
-        <v>6</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:56:32</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>37</v>
-      </c>
-      <c r="B21" t="n">
-        <v>6</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:56:22</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>36</v>
-      </c>
-      <c r="B22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:56:17</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>35</v>
-      </c>
-      <c r="B23" t="n">
-        <v>6</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:56:13</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>34</v>
-      </c>
-      <c r="B24" t="n">
-        <v>6</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:56:06</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>33</v>
-      </c>
-      <c r="B25" t="n">
-        <v>6</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:56:05</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:56:01</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>31</v>
-      </c>
-      <c r="B27" t="n">
-        <v>6</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:55:51</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>30</v>
-      </c>
-      <c r="B28" t="n">
-        <v>6</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:55:37</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>29</v>
-      </c>
-      <c r="B29" t="n">
-        <v>6</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:55:08</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:54:55</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:54:53</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>26</v>
-      </c>
-      <c r="B32" t="n">
-        <v>6</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:54:52</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" t="n">
-        <v>6</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:54:40</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>24</v>
-      </c>
-      <c r="B34" t="n">
-        <v>6</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Kamera 1</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025-08-15 12:54:03</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Orang meninggalkan ruangan</t>
+          <t>Orang ada di tempat</t>
         </is>
       </c>
     </row>
